--- a/astro-site/public/dl/kit-plan-financiero/04-presupuesto-inversion-capex.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/04-presupuesto-inversion-capex.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Obra" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Equipamiento Cocina" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mobiliario Sala" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tecnología" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Licencias" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Resumen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obra" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipamiento Cocina" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobiliario Sala" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tecnología" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencias" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Obra'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Equipamiento Cocina'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mobiliario Sala'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Tecnología'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Licencias'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Resumen'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,8 +30,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.0%" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -146,42 +153,42 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="12" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -541,15 +548,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="85"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -557,6 +565,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -564,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -599,9 +609,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -616,8 +624,25 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -626,16 +651,16 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="35"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="30"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -652,6 +677,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -693,7 +719,7 @@
       </c>
       <c r="D5" s="9">
         <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
@@ -711,7 +737,7 @@
       </c>
       <c r="D6" s="9">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="7" t="n"/>
     </row>
@@ -729,7 +755,7 @@
       </c>
       <c r="D7" s="9">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="7" t="n"/>
     </row>
@@ -747,7 +773,7 @@
       </c>
       <c r="D8" s="9">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="7" t="n"/>
     </row>
@@ -765,7 +791,7 @@
       </c>
       <c r="D9" s="9">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="7" t="n"/>
     </row>
@@ -783,7 +809,7 @@
       </c>
       <c r="D10" s="9">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -801,7 +827,7 @@
       </c>
       <c r="D11" s="9">
         <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
@@ -819,7 +845,7 @@
       </c>
       <c r="D12" s="9">
         <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E12" s="7" t="n"/>
     </row>
@@ -837,7 +863,7 @@
       </c>
       <c r="D13" s="9">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="7" t="n"/>
     </row>
@@ -855,7 +881,7 @@
       </c>
       <c r="D14" s="9">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="7" t="n"/>
     </row>
@@ -867,17 +893,18 @@
       </c>
       <c r="B15" s="11">
         <f>SUM(B5:B14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C15" s="11">
         <f>SUM(C5:C14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D15" s="9">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
@@ -891,7 +918,16 @@
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -900,16 +936,16 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="35"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="30"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -926,6 +962,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -967,7 +1004,7 @@
       </c>
       <c r="D5" s="9">
         <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
@@ -985,7 +1022,7 @@
       </c>
       <c r="D6" s="9">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="7" t="n"/>
     </row>
@@ -1003,7 +1040,7 @@
       </c>
       <c r="D7" s="9">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="7" t="n"/>
     </row>
@@ -1021,7 +1058,7 @@
       </c>
       <c r="D8" s="9">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="7" t="n"/>
     </row>
@@ -1039,7 +1076,7 @@
       </c>
       <c r="D9" s="9">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="7" t="n"/>
     </row>
@@ -1057,7 +1094,7 @@
       </c>
       <c r="D10" s="9">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -1075,7 +1112,7 @@
       </c>
       <c r="D11" s="9">
         <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
@@ -1093,7 +1130,7 @@
       </c>
       <c r="D12" s="9">
         <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E12" s="7" t="n"/>
     </row>
@@ -1111,7 +1148,7 @@
       </c>
       <c r="D13" s="9">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="7" t="n"/>
     </row>
@@ -1129,7 +1166,7 @@
       </c>
       <c r="D14" s="9">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="7" t="n"/>
     </row>
@@ -1141,17 +1178,18 @@
       </c>
       <c r="B15" s="11">
         <f>SUM(B5:B14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C15" s="11">
         <f>SUM(C5:C14)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D15" s="9">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
@@ -1165,7 +1203,16 @@
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1174,16 +1221,16 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="35"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="30"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,6 +1247,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1241,7 +1289,7 @@
       </c>
       <c r="D5" s="9">
         <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
@@ -1259,7 +1307,7 @@
       </c>
       <c r="D6" s="9">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="7" t="n"/>
     </row>
@@ -1277,7 +1325,7 @@
       </c>
       <c r="D7" s="9">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="7" t="n"/>
     </row>
@@ -1295,7 +1343,7 @@
       </c>
       <c r="D8" s="9">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="7" t="n"/>
     </row>
@@ -1313,7 +1361,7 @@
       </c>
       <c r="D9" s="9">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="7" t="n"/>
     </row>
@@ -1331,7 +1379,7 @@
       </c>
       <c r="D10" s="9">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -1349,7 +1397,7 @@
       </c>
       <c r="D11" s="9">
         <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
@@ -1367,7 +1415,7 @@
       </c>
       <c r="D12" s="9">
         <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E12" s="7" t="n"/>
     </row>
@@ -1379,17 +1427,18 @@
       </c>
       <c r="B13" s="11">
         <f>SUM(B5:B12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C13" s="11">
         <f>SUM(C5:C12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="9">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
@@ -1403,7 +1452,16 @@
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1412,16 +1470,16 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="35"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="30"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1438,6 +1496,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1479,7 +1538,7 @@
       </c>
       <c r="D5" s="9">
         <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
@@ -1497,7 +1556,7 @@
       </c>
       <c r="D6" s="9">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="7" t="n"/>
     </row>
@@ -1515,7 +1574,7 @@
       </c>
       <c r="D7" s="9">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="7" t="n"/>
     </row>
@@ -1533,7 +1592,7 @@
       </c>
       <c r="D8" s="9">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="7" t="n"/>
     </row>
@@ -1551,7 +1610,7 @@
       </c>
       <c r="D9" s="9">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="7" t="n"/>
     </row>
@@ -1569,7 +1628,7 @@
       </c>
       <c r="D10" s="9">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -1587,7 +1646,7 @@
       </c>
       <c r="D11" s="9">
         <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
@@ -1605,7 +1664,7 @@
       </c>
       <c r="D12" s="9">
         <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E12" s="7" t="n"/>
     </row>
@@ -1617,17 +1676,18 @@
       </c>
       <c r="B13" s="11">
         <f>SUM(B5:B12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C13" s="11">
         <f>SUM(C5:C12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="9">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
@@ -1641,7 +1701,16 @@
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1650,16 +1719,16 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="35"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="30"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1676,6 +1745,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1717,7 +1787,7 @@
       </c>
       <c r="D5" s="9">
         <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
@@ -1735,7 +1805,7 @@
       </c>
       <c r="D6" s="9">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="7" t="n"/>
     </row>
@@ -1753,7 +1823,7 @@
       </c>
       <c r="D7" s="9">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="7" t="n"/>
     </row>
@@ -1771,7 +1841,7 @@
       </c>
       <c r="D8" s="9">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="7" t="n"/>
     </row>
@@ -1789,7 +1859,7 @@
       </c>
       <c r="D9" s="9">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="7" t="n"/>
     </row>
@@ -1807,7 +1877,7 @@
       </c>
       <c r="D10" s="9">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
@@ -1825,7 +1895,7 @@
       </c>
       <c r="D11" s="9">
         <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
@@ -1843,7 +1913,7 @@
       </c>
       <c r="D12" s="9">
         <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E12" s="7" t="n"/>
     </row>
@@ -1861,7 +1931,7 @@
       </c>
       <c r="D13" s="9">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="7" t="n"/>
     </row>
@@ -1873,17 +1943,18 @@
       </c>
       <c r="B14" s="11">
         <f>SUM(B5:B13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C14" s="11">
         <f>SUM(C5:C13)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="9">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
@@ -1897,7 +1968,16 @@
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1906,15 +1986,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="30"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1931,6 +2011,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1961,15 +2042,15 @@
       </c>
       <c r="B5" s="13">
         <f>'Obra'!B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C5" s="13">
         <f>'Obra'!C15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D5" s="9">
         <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -1980,15 +2061,15 @@
       </c>
       <c r="B6" s="13">
         <f>'Equipamiento Cocina'!B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C6" s="13">
         <f>'Equipamiento Cocina'!C15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D6" s="9">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -1999,15 +2080,15 @@
       </c>
       <c r="B7" s="13">
         <f>'Mobiliario Sala'!B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C7" s="13">
         <f>'Mobiliario Sala'!C13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D7" s="9">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -2018,15 +2099,15 @@
       </c>
       <c r="B8" s="13">
         <f>'Tecnología'!B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C8" s="13">
         <f>'Tecnología'!C13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D8" s="9">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -2037,15 +2118,15 @@
       </c>
       <c r="B9" s="13">
         <f>'Licencias'!B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C9" s="13">
         <f>'Licencias'!C14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D9" s="9">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -2056,17 +2137,19 @@
       </c>
       <c r="B10" s="15">
         <f>SUM(B5:B9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="15">
         <f>SUM(C5:C9)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="9">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
@@ -2080,6 +2163,15 @@
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-plan-financiero/04-presupuesto-inversion-capex.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/04-presupuesto-inversion-capex.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobiliario Sala" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tecnología" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencias" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Otros conceptos de apertura" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Obra'!$4:$4</definedName>
@@ -21,7 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mobiliario Sala'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Tecnología'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Licencias'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Resumen'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Resumen'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +34,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +109,34 @@
       <color rgb="00FFD700"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +153,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -155,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,10 +221,91 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -258,6 +376,155 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Presupuesto (base) vs real por categoría</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Resumen'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Resumen'!$A$5:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Resumen'!$B$5:$B$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Resumen'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Resumen'!$A$5:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Resumen'!$E$5:$E$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>€</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,11 +817,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -591,7 +858,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>▸ Introduce el presupuesto estimado y luego el coste real.</t>
+          <t>▸ Cada partida lleva Base, IVA % e IVA (€): el desembolso real es la columna «Total con IVA», que con un 21 % es un quinto más de lo que enseña el presupuesto.</t>
         </is>
       </c>
     </row>
@@ -620,19 +887,54 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>▸ Obra civil, Equipamiento Cocina, Mobiliario Sala, Tecnología, Licencias y Permisos.</t>
+          <t>▸ Obra, Equipamiento Cocina, Mobiliario Sala, Tecnología, Licencias.</t>
         </is>
       </c>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+      <c r="B15" s="4" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>▸ El coeficiente de amortización por pestaña (obra 3 %, cocina 12 %, mobiliario 10 %, tecnología 25 %) da la dotación anual que pide el 07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>▸ Lo que no es CAPEX —traspaso, fianza, stock inicial, nóminas pre-apertura, imprevistos y fondo de maniobra— va en la pestaña 'Otros conceptos de apertura'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -653,14 +955,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -679,27 +986,52 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Presupuesto (€)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Base (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>IVA %</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>IVA (€)</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Total con IVA (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Real (€)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Desviación %</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Coef. amortización</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Dotación anual (€)</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -711,17 +1043,35 @@
           <t>Demolición y vaciado</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9">
-        <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
+      <c r="B5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D5" s="21">
+        <f>$B5*$C5</f>
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="22">
+        <f>$B5+$D5</f>
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(($F5-$B5)/$B5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I5" s="26">
+        <f>$B5*$H5</f>
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -729,17 +1079,35 @@
           <t>Albañilería</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9">
-        <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="7" t="n"/>
+      <c r="B6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D6" s="21">
+        <f>$B6*$C6</f>
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="22">
+        <f>$B6+$D6</f>
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
+        <f>IFERROR(($F6-$B6)/$B6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I6" s="26">
+        <f>$B6*$H6</f>
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -747,17 +1115,35 @@
           <t>Fontanería</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
-        <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
+      <c r="B7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D7" s="21">
+        <f>$B7*$C7</f>
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="22">
+        <f>$B7+$D7</f>
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(($F7-$B7)/$B7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I7" s="26">
+        <f>$B7*$H7</f>
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -765,17 +1151,35 @@
           <t>Electricidad</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="B8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D8" s="21">
+        <f>$B8*$C8</f>
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="22">
+        <f>$B8+$D8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24">
+        <f>IFERROR(($F8-$B8)/$B8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I8" s="26">
+        <f>$B8*$H8</f>
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -783,17 +1187,35 @@
           <t>Climatización / Extracción</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="B9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D9" s="21">
+        <f>$B9*$C9</f>
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="22">
+        <f>$B9+$D9</f>
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(($F9-$B9)/$B9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I9" s="26">
+        <f>$B9*$H9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -801,17 +1223,35 @@
           <t>Pintura y acabados</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="B10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D10" s="21">
+        <f>$B10*$C10</f>
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="22">
+        <f>$B10+$D10</f>
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <f>IFERROR(($F10-$B10)/$B10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I10" s="26">
+        <f>$B10*$H10</f>
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -819,17 +1259,35 @@
           <t>Suelo</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
-        <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
+      <c r="B11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D11" s="21">
+        <f>$B11*$C11</f>
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="22">
+        <f>$B11+$D11</f>
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(($F11-$B11)/$B11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I11" s="26">
+        <f>$B11*$H11</f>
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -837,17 +1295,35 @@
           <t>Fachada / Rótulo</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="7" t="n"/>
+      <c r="B12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D12" s="21">
+        <f>$B12*$C12</f>
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="22">
+        <f>$B12+$D12</f>
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24">
+        <f>IFERROR(($F12-$B12)/$B12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I12" s="26">
+        <f>$B12*$H12</f>
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -855,17 +1331,35 @@
           <t>Baños clientes</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
+      <c r="B13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D13" s="21">
+        <f>$B13*$C13</f>
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="22">
+        <f>$B13+$D13</f>
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(($F13-$B13)/$B13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I13" s="26">
+        <f>$B13*$H13</f>
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="27" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -873,51 +1367,114 @@
           <t>Vestuarios personal</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9">
-        <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E14" s="7" t="n"/>
+      <c r="B14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D14" s="21">
+        <f>$B14*$C14</f>
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="22">
+        <f>$B14+$D14</f>
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="24">
+        <f>IFERROR(($F14-$B14)/$B14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I14" s="26">
+        <f>$B14*$H14</f>
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="27" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>TOTAL OBRA</t>
         </is>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="29">
         <f>SUM(B5:B14)</f>
         <v>0.0</v>
       </c>
-      <c r="C15" s="11">
-        <f>SUM(C5:C14)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="9">
-        <f>IF(B15=0,0,(C15-B15)/B15)</f>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="29">
+        <f>SUM(D5:D14)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="31">
+        <f>SUM(E5:E14)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="31">
+        <f>SUM(F5:F14)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="24">
+        <f>IFERROR(($F15-$B15)/$B15,"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="31">
+        <f>SUM(I5:I14)</f>
         <v>0.0</v>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <mergeCells count="3">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -938,14 +1495,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -964,27 +1526,52 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Presupuesto (€)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Base (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>IVA %</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>IVA (€)</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Total con IVA (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Real (€)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Desviación %</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Coef. amortización</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Dotación anual (€)</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -996,17 +1583,35 @@
           <t>Cocina industrial (fogones)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9">
-        <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
+      <c r="B5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D5" s="21">
+        <f>$B5*$C5</f>
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="22">
+        <f>$B5+$D5</f>
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(($F5-$B5)/$B5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I5" s="26">
+        <f>$B5*$H5</f>
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1014,17 +1619,35 @@
           <t>Horno combinado</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9">
-        <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="7" t="n"/>
+      <c r="B6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D6" s="21">
+        <f>$B6*$C6</f>
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="22">
+        <f>$B6+$D6</f>
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
+        <f>IFERROR(($F6-$B6)/$B6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I6" s="26">
+        <f>$B6*$H6</f>
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1032,17 +1655,35 @@
           <t>Plancha / Grill</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
-        <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
+      <c r="B7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D7" s="21">
+        <f>$B7*$C7</f>
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="22">
+        <f>$B7+$D7</f>
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(($F7-$B7)/$B7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I7" s="26">
+        <f>$B7*$H7</f>
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1050,17 +1691,35 @@
           <t>Freidora</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="B8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D8" s="21">
+        <f>$B8*$C8</f>
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="22">
+        <f>$B8+$D8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24">
+        <f>IFERROR(($F8-$B8)/$B8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I8" s="26">
+        <f>$B8*$H8</f>
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1068,17 +1727,35 @@
           <t>Cámara frigorífica</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="B9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D9" s="21">
+        <f>$B9*$C9</f>
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="22">
+        <f>$B9+$D9</f>
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(($F9-$B9)/$B9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I9" s="26">
+        <f>$B9*$H9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1086,17 +1763,35 @@
           <t>Congelador</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="B10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D10" s="21">
+        <f>$B10*$C10</f>
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="22">
+        <f>$B10+$D10</f>
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <f>IFERROR(($F10-$B10)/$B10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I10" s="26">
+        <f>$B10*$H10</f>
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1104,17 +1799,35 @@
           <t>Mesa de trabajo inox</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
-        <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
+      <c r="B11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D11" s="21">
+        <f>$B11*$C11</f>
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="22">
+        <f>$B11+$D11</f>
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(($F11-$B11)/$B11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I11" s="26">
+        <f>$B11*$H11</f>
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1122,17 +1835,35 @@
           <t>Lavavajillas industrial</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="7" t="n"/>
+      <c r="B12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D12" s="21">
+        <f>$B12*$C12</f>
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="22">
+        <f>$B12+$D12</f>
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24">
+        <f>IFERROR(($F12-$B12)/$B12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I12" s="26">
+        <f>$B12*$H12</f>
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1140,17 +1871,35 @@
           <t>Campana extractora</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
+      <c r="B13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D13" s="21">
+        <f>$B13*$C13</f>
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="22">
+        <f>$B13+$D13</f>
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(($F13-$B13)/$B13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I13" s="26">
+        <f>$B13*$H13</f>
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="27" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1158,51 +1907,183 @@
           <t>Pequeño material cocina</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9">
-        <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E14" s="7" t="n"/>
+      <c r="B14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D14" s="21">
+        <f>$B14*$C14</f>
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="22">
+        <f>$B14+$D14</f>
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="24">
+        <f>IFERROR(($F14-$B14)/$B14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I14" s="26">
+        <f>$B14*$H14</f>
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="27" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>Menaje y utillaje de cocina (gastronorms, cuchillería)</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="34" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D15" s="21">
+        <f>$B15*$C15</f>
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="26">
+        <f>$B15+$D15</f>
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="24">
+        <f>IFERROR(($F15-$B15)/$B15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I15" s="26">
+        <f>$B15*$H15</f>
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="27" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Estantería de almacén y cámara de bebidas</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D16" s="26">
+        <f>$B16*$C16</f>
+        <v>0.0</v>
+      </c>
+      <c r="E16" s="26">
+        <f>$B16+$D16</f>
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="24">
+        <f>IFERROR(($F16-$B16)/$B16,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I16" s="26">
+        <f>$B16*$H16</f>
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="27" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
           <t>TOTAL EQUIPAMIENTO COCINA</t>
         </is>
       </c>
-      <c r="B15" s="11">
-        <f>SUM(B5:B14)</f>
-        <v>0.0</v>
-      </c>
-      <c r="C15" s="11">
-        <f>SUM(C5:C14)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="9">
-        <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="B17" s="31">
+        <f>SUM(B5:B16)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="31">
+        <f>SUM(D5:D16)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E17" s="31">
+        <f>SUM(E5:E16)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="31">
+        <f>SUM(F5:F16)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="24">
+        <f>IFERROR(($F17-$B17)/$B17,"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="31">
+        <f>SUM(I5:I16)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <mergeCells count="3">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1223,14 +2104,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1249,27 +2135,52 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Presupuesto (€)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Base (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>IVA %</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>IVA (€)</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Total con IVA (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Real (€)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Desviación %</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Coef. amortización</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Dotación anual (€)</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -1281,17 +2192,35 @@
           <t>Mesas</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9">
-        <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
+      <c r="B5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D5" s="21">
+        <f>$B5*$C5</f>
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="22">
+        <f>$B5+$D5</f>
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(($F5-$B5)/$B5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="26">
+        <f>$B5*$H5</f>
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1299,17 +2228,35 @@
           <t>Sillas</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9">
-        <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="7" t="n"/>
+      <c r="B6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D6" s="21">
+        <f>$B6*$C6</f>
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="22">
+        <f>$B6+$D6</f>
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
+        <f>IFERROR(($F6-$B6)/$B6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="26">
+        <f>$B6*$H6</f>
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1317,17 +2264,35 @@
           <t>Barra</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
-        <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
+      <c r="B7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D7" s="21">
+        <f>$B7*$C7</f>
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="22">
+        <f>$B7+$D7</f>
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(($F7-$B7)/$B7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="26">
+        <f>$B7*$H7</f>
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1335,17 +2300,35 @@
           <t>Taburetes barra</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="B8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D8" s="21">
+        <f>$B8*$C8</f>
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="22">
+        <f>$B8+$D8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24">
+        <f>IFERROR(($F8-$B8)/$B8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="26">
+        <f>$B8*$H8</f>
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1353,17 +2336,35 @@
           <t>Estanterías / decoración</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="B9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D9" s="21">
+        <f>$B9*$C9</f>
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="22">
+        <f>$B9+$D9</f>
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(($F9-$B9)/$B9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="26">
+        <f>$B9*$H9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1371,17 +2372,35 @@
           <t>Iluminación</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="B10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D10" s="21">
+        <f>$B10*$C10</f>
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="22">
+        <f>$B10+$D10</f>
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <f>IFERROR(($F10-$B10)/$B10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="26">
+        <f>$B10*$H10</f>
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1389,17 +2408,35 @@
           <t>Terraza (mesas + sillas)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
-        <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
+      <c r="B11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D11" s="21">
+        <f>$B11*$C11</f>
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="22">
+        <f>$B11+$D11</f>
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(($F11-$B11)/$B11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="26">
+        <f>$B11*$H11</f>
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1407,51 +2444,185 @@
           <t>Textil (manteles, servilletas)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="7" t="n"/>
+      <c r="B12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D12" s="21">
+        <f>$B12*$C12</f>
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="22">
+        <f>$B12+$D12</f>
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24">
+        <f>IFERROR(($F12-$B12)/$B12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="26">
+        <f>$B12*$H12</f>
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>Vajilla, cristalería y cubertería (con reposición)</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D13" s="21">
+        <f>$B13*$C13</f>
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="26">
+        <f>$B13+$D13</f>
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(($F13-$B13)/$B13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="26">
+        <f>$B13*$H13</f>
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Uniformes y EPI</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D14" s="26">
+        <f>$B14*$C14</f>
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="26">
+        <f>$B14+$D14</f>
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="24">
+        <f>IFERROR(($F14-$B14)/$B14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="26">
+        <f>$B14*$H14</f>
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="27" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
           <t>TOTAL MOBILIARIO SALA</t>
         </is>
       </c>
-      <c r="B13" s="11">
-        <f>SUM(B5:B12)</f>
-        <v>0.0</v>
-      </c>
-      <c r="C13" s="11">
-        <f>SUM(C5:C12)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="9">
-        <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="B15" s="31">
+        <f>SUM(B5:B14)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" s="31">
+        <f>SUM(D5:D14)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="31">
+        <f>SUM(E5:E14)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="31">
+        <f>SUM(F5:F14)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="24">
+        <f>IFERROR(($F15-$B15)/$B15,"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="31">
+        <f>SUM(I5:I14)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <mergeCells count="3">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1472,14 +2643,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1498,27 +2674,52 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Presupuesto (€)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Base (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>IVA %</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>IVA (€)</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Total con IVA (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Real (€)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Desviación %</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Coef. amortización</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Dotación anual (€)</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -1530,17 +2731,35 @@
           <t>TPV (hardware + software)</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9">
-        <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
+      <c r="B5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D5" s="21">
+        <f>$B5*$C5</f>
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="22">
+        <f>$B5+$D5</f>
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(($F5-$B5)/$B5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I5" s="26">
+        <f>$B5*$H5</f>
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1548,17 +2767,35 @@
           <t>Impresoras comandas</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9">
-        <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="7" t="n"/>
+      <c r="B6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D6" s="21">
+        <f>$B6*$C6</f>
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="22">
+        <f>$B6+$D6</f>
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
+        <f>IFERROR(($F6-$B6)/$B6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I6" s="26">
+        <f>$B6*$H6</f>
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1566,17 +2803,35 @@
           <t>Datáfono</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
-        <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
+      <c r="B7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D7" s="21">
+        <f>$B7*$C7</f>
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="22">
+        <f>$B7+$D7</f>
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(($F7-$B7)/$B7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I7" s="26">
+        <f>$B7*$H7</f>
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1584,17 +2839,35 @@
           <t>Sistema de reservas</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="B8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D8" s="21">
+        <f>$B8*$C8</f>
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="22">
+        <f>$B8+$D8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24">
+        <f>IFERROR(($F8-$B8)/$B8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I8" s="26">
+        <f>$B8*$H8</f>
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1602,17 +2875,35 @@
           <t>Wifi / Red</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="B9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D9" s="21">
+        <f>$B9*$C9</f>
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="22">
+        <f>$B9+$D9</f>
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(($F9-$B9)/$B9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I9" s="26">
+        <f>$B9*$H9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1620,17 +2911,35 @@
           <t>Pantallas / Digital signage</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="B10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D10" s="21">
+        <f>$B10*$C10</f>
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="22">
+        <f>$B10+$D10</f>
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <f>IFERROR(($F10-$B10)/$B10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I10" s="26">
+        <f>$B10*$H10</f>
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1638,17 +2947,35 @@
           <t>Web / App delivery</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
-        <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
+      <c r="B11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D11" s="21">
+        <f>$B11*$C11</f>
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="22">
+        <f>$B11+$D11</f>
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(($F11-$B11)/$B11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I11" s="26">
+        <f>$B11*$H11</f>
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1656,51 +2983,116 @@
           <t>Sistema de seguridad (cámaras)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="7" t="n"/>
+      <c r="B12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D12" s="21">
+        <f>$B12*$C12</f>
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="22">
+        <f>$B12+$D12</f>
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24">
+        <f>IFERROR(($F12-$B12)/$B12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I12" s="26">
+        <f>$B12*$H12</f>
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>TOTAL TECNOLOGÍA</t>
         </is>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="29">
         <f>SUM(B5:B12)</f>
         <v>0.0</v>
       </c>
-      <c r="C13" s="11">
-        <f>SUM(C5:C12)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="9">
-        <f>IF(B13=0,0,(C13-B13)/B13)</f>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="29">
+        <f>SUM(D5:D12)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="31">
+        <f>SUM(E5:E12)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="31">
+        <f>SUM(F5:F12)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(($F13-$B13)/$B13,"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="31">
+        <f>SUM(I5:I12)</f>
         <v>0.0</v>
       </c>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <mergeCells count="3">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 F5 F6 F7 F8 F9 F10 F11 F12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 H5 H6 H7 H8 H9 H10 H11 H12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1721,14 +3113,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1747,27 +3144,52 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Partida</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Presupuesto (€)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Base (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>IVA %</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>IVA (€)</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Total con IVA (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Real (€)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>Desviación %</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Coef. amortización</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Dotación anual (€)</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
@@ -1779,17 +3201,35 @@
           <t>Licencia de apertura</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9">
-        <f>IF(B5=0,0,(C5-B5)/B5)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="7" t="n"/>
+      <c r="B5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21">
+        <f>$B5*$C5</f>
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="22">
+        <f>$B5+$D5</f>
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(($F5-$B5)/$B5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="26">
+        <f>$B5*$H5</f>
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1797,17 +3237,35 @@
           <t>Licencia de obras</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9">
-        <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="7" t="n"/>
+      <c r="B6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="21">
+        <f>$B6*$C6</f>
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="22">
+        <f>$B6+$D6</f>
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
+        <f>IFERROR(($F6-$B6)/$B6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="26">
+        <f>$B6*$H6</f>
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1815,17 +3273,35 @@
           <t>Proyecto técnico (arquitecto)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9">
-        <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="7" t="n"/>
+      <c r="B7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21">
+        <f>$B7*$C7</f>
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="22">
+        <f>$B7+$D7</f>
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(($F7-$B7)/$B7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="26">
+        <f>$B7*$H7</f>
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1833,17 +3309,35 @@
           <t>Certificado energético</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="B8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="21">
+        <f>$B8*$C8</f>
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="22">
+        <f>$B8+$D8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24">
+        <f>IFERROR(($F8-$B8)/$B8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="26">
+        <f>$B8*$H8</f>
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="27" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1851,17 +3345,35 @@
           <t>Plan de autoprotección</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9">
-        <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="B9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21">
+        <f>$B9*$C9</f>
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="22">
+        <f>$B9+$D9</f>
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(($F9-$B9)/$B9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="26">
+        <f>$B9*$H9</f>
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="27" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1869,17 +3381,35 @@
           <t>Alta Hacienda / SS</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="B10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="21">
+        <f>$B10*$C10</f>
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="22">
+        <f>$B10+$D10</f>
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <f>IFERROR(($F10-$B10)/$B10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="26">
+        <f>$B10*$H10</f>
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1887,17 +3417,35 @@
           <t>Registro sanitario</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
-        <f>IF(B11=0,0,(C11-B11)/B11)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="7" t="n"/>
+      <c r="B11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21">
+        <f>$B11*$C11</f>
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="22">
+        <f>$B11+$D11</f>
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(($F11-$B11)/$B11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="26">
+        <f>$B11*$H11</f>
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1905,69 +3453,123 @@
           <t>SGAE / Derechos música</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9">
-        <f>IF(B12=0,0,(C12-B12)/B12)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="7" t="n"/>
+      <c r="B12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="21">
+        <f>$B12*$C12</f>
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="22">
+        <f>$B12+$D12</f>
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24">
+        <f>IFERROR(($F12-$B12)/$B12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="26">
+        <f>$B12*$H12</f>
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Seguros (año 1)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="7" t="n"/>
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>TOTAL LICENCIAS</t>
+        </is>
+      </c>
+      <c r="B13" s="29">
+        <f>SUM(B5:B12)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="29">
+        <f>SUM(D5:D12)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="38">
+        <f>SUM(E5:E12)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="31">
+        <f>SUM(F5:F12)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(($F13-$B13)/$B13,"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="31">
+        <f>SUM(I5:I12)</f>
+        <v>0.0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL LICENCIAS</t>
-        </is>
-      </c>
-      <c r="B14" s="11">
-        <f>SUM(B5:B13)</f>
-        <v>0.0</v>
-      </c>
-      <c r="C14" s="11">
-        <f>SUM(C5:C13)</f>
-        <v>0.0</v>
-      </c>
-      <c r="D14" s="9">
-        <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="39" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>© 2026 AI Chef Pro · aichef.pro</t>
-        </is>
-      </c>
-    </row>
+      <c r="A16" s="12" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
-  <mergeCells count="3">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 F5 F6 F7 F8 F9 F10 F11 F12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 H5 H6 H7 H8 H9 H10 H11 H12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1984,17 +3586,460 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>Otros conceptos de apertura — lo que no es CAPEX y hay que pagar igual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Kit Plan Financiero para Restaurantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Base (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>IVA %</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>IVA (€)</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Total con IVA (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>Real (€)</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Desviación %</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Traspaso del local</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D5" s="26">
+        <f>$B5*$C5</f>
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="26">
+        <f>$B5+$D5</f>
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(($F5-$B5)/$B5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="42" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fianza y primeras rentas</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="26">
+        <f>$B6*$C6</f>
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="26">
+        <f>$B6+$D6</f>
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
+        <f>IFERROR(($F6-$B6)/$B6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="42" t="inlineStr">
+        <is>
+          <t>La fianza se recupera al salir; las rentas anticipadas, no.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Constitución, notaría y registro</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D7" s="26">
+        <f>$B7*$C7</f>
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="26">
+        <f>$B7+$D7</f>
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(($F7-$B7)/$B7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="42" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STOCK INICIAL de despensa y bodega</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="26">
+        <f>$B8*$C8</f>
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="26">
+        <f>$B8+$D8</f>
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24">
+        <f>IFERROR(($F8-$B8)/$B8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="42" t="inlineStr">
+        <is>
+          <t>Semanas de consumo × coste diario de materia prima. En un casual de 60 plazas, 2-4 semanas suelen ser 8.000-15.000 €.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nóminas y formación pre-apertura</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="26">
+        <f>$B9*$C9</f>
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="26">
+        <f>$B9+$D9</f>
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(($F9-$B9)/$B9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="42" t="inlineStr">
+        <is>
+          <t>Las dos o tres semanas de plantilla antes de facturar el primer euro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Marketing de lanzamiento</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D10" s="26">
+        <f>$B10*$C10</f>
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="26">
+        <f>$B10+$D10</f>
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24">
+        <f>IFERROR(($F10-$B10)/$B10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="42" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Seguros (año 1)</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="26">
+        <f>$B11*$C11</f>
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="26">
+        <f>$B11+$D11</f>
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(($F11-$B11)/$B11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="42" t="inlineStr">
+        <is>
+          <t>Gasto anticipado NO amortizable. Venía de la pestaña Licencias: no es CAPEX y duplicaba 02!Datos!C8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Imprevistos (5-10 % de la inversión)</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="35" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D12" s="26">
+        <f>$B12*$C12</f>
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="26">
+        <f>$B12+$D12</f>
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="24">
+        <f>IFERROR(($F12-$B12)/$B12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="42" t="inlineStr">
+        <is>
+          <t>Sobre «INVERSIÓN TOTAL (CAPEX)» de la pestaña Resumen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FONDO DE MANIOBRA (3-6 meses de costes fijos)</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="26">
+        <f>$B13*$C13</f>
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="26">
+        <f>$B13+$D13</f>
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(($F13-$B13)/$B13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="42" t="inlineStr">
+        <is>
+          <t>Es lo que pide BONUS-09!C15 y hasta hoy no tenía dónde ponerse. Referencia: 02!Datos!C14 × 3 a 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>TOTAL OTROS CONCEPTOS DE APERTURA</t>
+        </is>
+      </c>
+      <c r="B14" s="31">
+        <f>SUM(B5:B13)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D14" s="31">
+        <f>SUM(D5:D13)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="31">
+        <f>SUM(E5:E13)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="31">
+        <f>SUM(F5:F13)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="24">
+        <f>IFERROR(($F14-$B14)/$B14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Ninguno de estos conceptos se amortiza: son gasto del ejercicio o circulante. Por eso no llevan coeficiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <dataValidations count="2">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 F5 F6 F7 F8 F9 F10 F11 F12 F13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2013,24 +4058,39 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Presupuesto (€)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Base (€)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>IVA (€)</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Total con IVA (€)</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
         <is>
           <t>Real (€)</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>Desviación %</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>Dotación anual (€)</t>
         </is>
       </c>
     </row>
@@ -2045,11 +4105,23 @@
         <v>0.0</v>
       </c>
       <c r="C5" s="13">
-        <f>'Obra'!C15</f>
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="9">
-        <f>IF(B5=0,0,(C5-B5)/B5)</f>
+        <f>'Obra'!D15</f>
+        <v>0.0</v>
+      </c>
+      <c r="D5" s="21">
+        <f>'Obra'!E15</f>
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="26">
+        <f>'Obra'!F15</f>
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="24">
+        <f>IFERROR(($E5-$B5)/$B5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="26">
+        <f>'Obra'!I15</f>
         <v>0.0</v>
       </c>
     </row>
@@ -2060,15 +4132,27 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>'Equipamiento Cocina'!B15</f>
+        <f>'Equipamiento Cocina'!B17</f>
         <v>0.0</v>
       </c>
       <c r="C6" s="13">
-        <f>'Equipamiento Cocina'!C15</f>
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="9">
-        <f>IF(B6=0,0,(C6-B6)/B6)</f>
+        <f>'Equipamiento Cocina'!D17</f>
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="21">
+        <f>'Equipamiento Cocina'!E17</f>
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="26">
+        <f>'Equipamiento Cocina'!F17</f>
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="24">
+        <f>IFERROR(($E6-$B6)/$B6,"")</f>
+        <v/>
+      </c>
+      <c r="G6" s="26">
+        <f>'Equipamiento Cocina'!I17</f>
         <v>0.0</v>
       </c>
     </row>
@@ -2079,15 +4163,27 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>'Mobiliario Sala'!B13</f>
+        <f>'Mobiliario Sala'!B15</f>
         <v>0.0</v>
       </c>
       <c r="C7" s="13">
-        <f>'Mobiliario Sala'!C13</f>
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="9">
-        <f>IF(B7=0,0,(C7-B7)/B7)</f>
+        <f>'Mobiliario Sala'!D15</f>
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="21">
+        <f>'Mobiliario Sala'!E15</f>
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="26">
+        <f>'Mobiliario Sala'!F15</f>
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="24">
+        <f>IFERROR(($E7-$B7)/$B7,"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="26">
+        <f>'Mobiliario Sala'!I15</f>
         <v>0.0</v>
       </c>
     </row>
@@ -2102,11 +4198,23 @@
         <v>0.0</v>
       </c>
       <c r="C8" s="13">
-        <f>'Tecnología'!C13</f>
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="9">
-        <f>IF(B8=0,0,(C8-B8)/B8)</f>
+        <f>'Tecnología'!D13</f>
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="21">
+        <f>'Tecnología'!E13</f>
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="26">
+        <f>'Tecnología'!F13</f>
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="24">
+        <f>IFERROR(($E8-$B8)/$B8,"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="26">
+        <f>'Tecnología'!I13</f>
         <v>0.0</v>
       </c>
     </row>
@@ -2117,52 +4225,172 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>'Licencias'!B14</f>
+        <f>'Licencias'!B13</f>
         <v>0.0</v>
       </c>
       <c r="C9" s="13">
-        <f>'Licencias'!C14</f>
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="9">
-        <f>IF(B9=0,0,(C9-B9)/B9)</f>
+        <f>'Licencias'!D13</f>
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="21">
+        <f>'Licencias'!E13</f>
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="26">
+        <f>'Licencias'!F13</f>
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="24">
+        <f>IFERROR(($E9-$B9)/$B9,"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="26">
+        <f>'Licencias'!I13</f>
         <v>0.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>INVERSIÓN TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="15">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>INVERSIÓN TOTAL (CAPEX)</t>
+        </is>
+      </c>
+      <c r="B10" s="29">
         <f>SUM(B5:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="29">
         <f>SUM(C5:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="9">
-        <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12"/>
+      <c r="D10" s="29">
+        <f>SUM(D5:D9)</f>
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="31">
+        <f>SUM(E5:E9)</f>
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="24">
+        <f>IFERROR(($E10-$B10)/$B10,"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="31">
+        <f>SUM(G5:G9)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Otros conceptos de apertura</t>
+        </is>
+      </c>
+      <c r="B11" s="26">
+        <f>'Otros conceptos de apertura'!B14</f>
+        <v>0.0</v>
+      </c>
+      <c r="C11" s="26">
+        <f>'Otros conceptos de apertura'!D14</f>
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="26">
+        <f>'Otros conceptos de apertura'!E14</f>
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="26">
+        <f>'Otros conceptos de apertura'!F14</f>
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="24">
+        <f>IFERROR(($E11-$B11)/$B11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>DESEMBOLSO TOTAL DE APERTURA (base + IVA)</t>
+        </is>
+      </c>
+      <c r="B12" s="31">
+        <f>B10+B11</f>
+        <v>0.0</v>
+      </c>
+      <c r="C12" s="31">
+        <f>C10+C11</f>
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="31">
+        <f>D10+D11</f>
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="31">
+        <f>E10+E11</f>
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="24">
+        <f>IFERROR(($E12-$B12)/$B12,"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="12" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>De dónde sale cada dato (el encadenado realista entre libros):</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>▸ La «Dotación anual (€)» de la fila 10 es la que se copia a 07!Proyecciones, fila «Amortización».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>▸ El «IVA (€)» de la fila 12 es IVA soportado: se recupera vía modelo 303, pero hay que ADELANTARLO. El préstamo tiene que cubrirlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="31"/>
+    <row r="32"/>
   </sheetData>
-  <mergeCells count="3">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <conditionalFormatting sqref="F5:F12">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>=ABS(F5)&gt;0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2173,5 +4401,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>